--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574783279</v>
+        <v>46157.93118879478</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118879478</v>
+        <v>46157.93184122849</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93184122849</v>
+        <v>46157.93406127091</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406127091</v>
+        <v>46157.93724167682</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724167682</v>
+        <v>46158.28221941572</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221941572</v>
+        <v>46158.29702977491</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29702977491</v>
+        <v>46158.29821763498</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821763498</v>
+        <v>46158.33392905762</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392905762</v>
+        <v>46158.36862692685</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862692685</v>
+        <v>46158.37293660243</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
